--- a/Grupo/MSPS_Grupo.xlsx
+++ b/Grupo/MSPS_Grupo.xlsx
@@ -461,13 +461,13 @@
         <v>44.33171670735739</v>
       </c>
       <c r="C2" s="2">
-        <v>114.5235025881233</v>
+        <v>114.521405143487</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>50.77023473070991</v>
+        <v>50.76930489749569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -518,7 +518,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>16.45978037886198</v>
+        <v>16.45978037886199</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2">
-        <v>1.516689650063091</v>
+        <v>1.516689650063092</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>5.263060937513938</v>
+        <v>5.263060937513939</v>
       </c>
       <c r="C11" s="2">
         <v>129.5874087390933</v>
@@ -620,7 +620,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="2">
-        <v>6.820264289283744</v>
+        <v>6.820264289283746</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -631,13 +631,13 @@
         <v>15.14296915673314</v>
       </c>
       <c r="C12" s="2">
-        <v>116.7115064440879</v>
+        <v>116.7115064440878</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>17.67358742318684</v>
+        <v>17.67358742318683</v>
       </c>
     </row>
     <row r="13" spans="1:5">
